--- a/artfynd/A 8457-2025 artfynd.xlsx
+++ b/artfynd/A 8457-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>128060692</v>
       </c>
       <c r="B2" t="n">
-        <v>92047</v>
+        <v>92048</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -891,6 +891,200 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128060715</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91124</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kitterödjan, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>485447</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6413277</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Aneby</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lommaryd</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128060714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91124</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kitterödjan, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>485484</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6413230</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Aneby</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lommaryd</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8457-2025 artfynd.xlsx
+++ b/artfynd/A 8457-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128060692</v>
+        <v>128060704</v>
       </c>
       <c r="B2" t="n">
-        <v>92048</v>
+        <v>57669</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3298</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kitterödjan, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>485492</v>
+        <v>485491</v>
       </c>
       <c r="R2" t="n">
-        <v>6413384</v>
+        <v>6413254</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,29 +754,8 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -796,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128060704</v>
+        <v>128060715</v>
       </c>
       <c r="B3" t="n">
-        <v>57669</v>
+        <v>91124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>3215</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>485491</v>
+        <v>485447</v>
       </c>
       <c r="R3" t="n">
-        <v>6413254</v>
+        <v>6413277</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128060715</v>
+        <v>128060714</v>
       </c>
       <c r="B4" t="n">
         <v>91124</v>
@@ -928,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>485447</v>
+        <v>485484</v>
       </c>
       <c r="R4" t="n">
-        <v>6413277</v>
+        <v>6413230</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,103 +963,6 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>128060714</v>
-      </c>
-      <c r="B5" t="n">
-        <v>91124</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>3215</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Rödgul trumpetsvamp</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Craterellus lutescens</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Kitterödjan, Sm</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>485484</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6413230</v>
-      </c>
-      <c r="S5" t="n">
-        <v>10</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Jönköping</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Aneby</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Lommaryd</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Gabriella Fjordmark Lerne</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Gabriella Fjordmark Lerne</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8457-2025 artfynd.xlsx
+++ b/artfynd/A 8457-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128060704</v>
       </c>
       <c r="B2" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128060715</v>
       </c>
       <c r="B3" t="n">
-        <v>91124</v>
+        <v>91133</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128060714</v>
       </c>
       <c r="B4" t="n">
-        <v>91124</v>
+        <v>91133</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8457-2025 artfynd.xlsx
+++ b/artfynd/A 8457-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128060704</v>
       </c>
       <c r="B2" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128060715</v>
       </c>
       <c r="B3" t="n">
-        <v>91133</v>
+        <v>91225</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128060714</v>
       </c>
       <c r="B4" t="n">
-        <v>91133</v>
+        <v>91225</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8457-2025 artfynd.xlsx
+++ b/artfynd/A 8457-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128060704</v>
       </c>
       <c r="B2" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128060715</v>
       </c>
       <c r="B3" t="n">
-        <v>91225</v>
+        <v>91237</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128060714</v>
       </c>
       <c r="B4" t="n">
-        <v>91225</v>
+        <v>91237</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8457-2025 artfynd.xlsx
+++ b/artfynd/A 8457-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128060715</v>
       </c>
       <c r="B3" t="n">
-        <v>91237</v>
+        <v>91239</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128060714</v>
       </c>
       <c r="B4" t="n">
-        <v>91237</v>
+        <v>91239</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8457-2025 artfynd.xlsx
+++ b/artfynd/A 8457-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128060715</v>
       </c>
       <c r="B3" t="n">
-        <v>91239</v>
+        <v>91240</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128060714</v>
       </c>
       <c r="B4" t="n">
-        <v>91239</v>
+        <v>91240</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8457-2025 artfynd.xlsx
+++ b/artfynd/A 8457-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128060715</v>
       </c>
       <c r="B3" t="n">
-        <v>91240</v>
+        <v>91267</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128060714</v>
       </c>
       <c r="B4" t="n">
-        <v>91240</v>
+        <v>91267</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8457-2025 artfynd.xlsx
+++ b/artfynd/A 8457-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128060715</v>
       </c>
       <c r="B3" t="n">
-        <v>91267</v>
+        <v>91277</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128060714</v>
       </c>
       <c r="B4" t="n">
-        <v>91267</v>
+        <v>91277</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8457-2025 artfynd.xlsx
+++ b/artfynd/A 8457-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,34 +675,30 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128060704</v>
+        <v>128060725</v>
       </c>
       <c r="B2" t="n">
-        <v>57686</v>
+        <v>97457</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>221944</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -710,10 +706,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>485491</v>
+        <v>485514</v>
       </c>
       <c r="R2" t="n">
-        <v>6413254</v>
+        <v>6413181</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,6 +750,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -772,32 +769,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128060715</v>
+        <v>128060704</v>
       </c>
       <c r="B3" t="n">
-        <v>91277</v>
+        <v>57686</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3215</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +804,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>485447</v>
+        <v>485491</v>
       </c>
       <c r="R3" t="n">
-        <v>6413277</v>
+        <v>6413254</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,7 +866,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128060714</v>
+        <v>128060715</v>
       </c>
       <c r="B4" t="n">
         <v>91277</v>
@@ -904,10 +901,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>485484</v>
+        <v>485447</v>
       </c>
       <c r="R4" t="n">
-        <v>6413230</v>
+        <v>6413277</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,6 +960,103 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128060714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91277</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kitterödjan, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>485484</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6413230</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Aneby</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lommaryd</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8457-2025 artfynd.xlsx
+++ b/artfynd/A 8457-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128060714</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128060715</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128060704</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1057,8 +1077,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128060725</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>